--- a/diseases/d203/2010-2014.xlsx
+++ b/diseases/d203/2010-2014.xlsx
@@ -16095,6 +16095,11 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16107,12 +16112,22 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -20553,6 +20568,11 @@
       <c r="R103" t="n">
         <v>0</v>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20565,12 +20585,22 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -20688,6 +20718,11 @@
       <c r="R104" t="n">
         <v>0</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20700,12 +20735,22 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -20823,6 +20868,11 @@
       <c r="R105" t="n">
         <v>0</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20835,12 +20885,22 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -20958,6 +21018,11 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20970,12 +21035,22 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -21093,6 +21168,11 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21105,12 +21185,22 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -21228,6 +21318,11 @@
       <c r="R108" t="n">
         <v>0</v>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21240,12 +21335,22 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -21363,6 +21468,11 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21375,12 +21485,22 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -21498,6 +21618,11 @@
       <c r="R110" t="n">
         <v>0</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21510,12 +21635,22 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -21633,6 +21768,11 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21645,12 +21785,22 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -21768,6 +21918,11 @@
       <c r="R112" t="n">
         <v>0</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21780,12 +21935,22 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -21903,6 +22068,11 @@
       <c r="R113" t="n">
         <v>0</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21915,12 +22085,22 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -27933,6 +28113,11 @@
       <c r="R144" t="n">
         <v>0</v>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27945,12 +28130,22 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -32391,6 +32586,11 @@
       <c r="R167" t="n">
         <v>0</v>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32403,12 +32603,22 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -32526,6 +32736,11 @@
       <c r="R168" t="n">
         <v>0</v>
       </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32538,12 +32753,22 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -32661,6 +32886,11 @@
       <c r="R169" t="n">
         <v>0</v>
       </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32673,12 +32903,22 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -32796,6 +33036,11 @@
       <c r="R170" t="n">
         <v>0</v>
       </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32808,12 +33053,22 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -32931,6 +33186,11 @@
       <c r="R171" t="n">
         <v>0</v>
       </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32943,12 +33203,22 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -33066,6 +33336,11 @@
       <c r="R172" t="n">
         <v>0</v>
       </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33078,12 +33353,22 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -33201,6 +33486,11 @@
       <c r="R173" t="n">
         <v>0</v>
       </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33213,12 +33503,22 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -33336,6 +33636,11 @@
       <c r="R174" t="n">
         <v>0</v>
       </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33348,12 +33653,22 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -33912,6 +34227,11 @@
       <c r="R178" t="n">
         <v>0</v>
       </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33924,12 +34244,22 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
         <v>0</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
@@ -34635,6 +34965,11 @@
       <c r="R183" t="n">
         <v>0</v>
       </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34647,12 +34982,22 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
         <v>0</v>
+      </c>
+      <c r="AU183" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
@@ -35358,6 +35703,11 @@
       <c r="R188" t="n">
         <v>0</v>
       </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35370,12 +35720,22 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
         <v>0</v>
+      </c>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
@@ -42123,6 +42483,11 @@
       <c r="R224" t="n">
         <v>0</v>
       </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42135,12 +42500,22 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
         <v>0</v>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
@@ -47169,6 +47544,11 @@
       <c r="R251" t="n">
         <v>0</v>
       </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47181,12 +47561,22 @@
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS251" t="inlineStr"/>
       <c r="AT251" t="n">
         <v>0</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
@@ -47892,6 +48282,11 @@
       <c r="R256" t="n">
         <v>0</v>
       </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47904,12 +48299,22 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS256" t="inlineStr"/>
       <c r="AT256" t="n">
         <v>0</v>
+      </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
@@ -48762,6 +49167,11 @@
       <c r="R262" t="n">
         <v>0</v>
       </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48774,12 +49184,22 @@
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS262" t="inlineStr"/>
       <c r="AT262" t="n">
         <v>0</v>
+      </c>
+      <c r="AU262" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
@@ -49485,6 +49905,11 @@
       <c r="R267" t="n">
         <v>0</v>
       </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49497,12 +49922,22 @@
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
         <v>0</v>
+      </c>
+      <c r="AU267" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
@@ -50208,6 +50643,11 @@
       <c r="R272" t="n">
         <v>0</v>
       </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA272" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50220,12 +50660,22 @@
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS272" t="inlineStr"/>
       <c r="AT272" t="n">
         <v>0</v>
+      </c>
+      <c r="AU272" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
@@ -51078,6 +51528,11 @@
       <c r="R278" t="n">
         <v>0</v>
       </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA278" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51090,12 +51545,22 @@
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR278" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS278" t="inlineStr"/>
       <c r="AT278" t="n">
         <v>0</v>
+      </c>
+      <c r="AU278" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
@@ -51801,6 +52266,11 @@
       <c r="R283" t="n">
         <v>0</v>
       </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA283" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51813,12 +52283,22 @@
       </c>
       <c r="AP283" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR283" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS283" t="inlineStr"/>
       <c r="AT283" t="n">
         <v>0</v>
+      </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV283" t="inlineStr">
         <is>
@@ -52671,6 +53151,11 @@
       <c r="R289" t="n">
         <v>0</v>
       </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA289" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52683,12 +53168,22 @@
       </c>
       <c r="AP289" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR289" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS289" t="inlineStr"/>
       <c r="AT289" t="n">
         <v>0</v>
+      </c>
+      <c r="AU289" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV289" t="inlineStr">
         <is>
@@ -53394,6 +53889,11 @@
       <c r="R294" t="n">
         <v>0</v>
       </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA294" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -53406,12 +53906,22 @@
       </c>
       <c r="AP294" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR294" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS294" t="inlineStr"/>
       <c r="AT294" t="n">
         <v>0</v>
+      </c>
+      <c r="AU294" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV294" t="inlineStr">
         <is>
@@ -54117,6 +54627,11 @@
       <c r="R299" t="n">
         <v>0</v>
       </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA299" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -54129,12 +54644,22 @@
       </c>
       <c r="AP299" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR299" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS299" t="inlineStr"/>
       <c r="AT299" t="n">
         <v>0</v>
+      </c>
+      <c r="AU299" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV299" t="inlineStr">
         <is>
@@ -54987,6 +55512,11 @@
       <c r="R305" t="n">
         <v>0</v>
       </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA305" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -54999,12 +55529,22 @@
       </c>
       <c r="AP305" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR305" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS305" t="inlineStr"/>
       <c r="AT305" t="n">
         <v>0</v>
+      </c>
+      <c r="AU305" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV305" t="inlineStr">
         <is>
@@ -61605,6 +62145,11 @@
       <c r="R340" t="n">
         <v>0</v>
       </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA340" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -61617,12 +62162,22 @@
       </c>
       <c r="AP340" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR340" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS340" t="inlineStr"/>
       <c r="AT340" t="n">
         <v>0</v>
+      </c>
+      <c r="AU340" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV340" t="inlineStr">
         <is>
@@ -66651,6 +67206,11 @@
       <c r="R367" t="n">
         <v>0</v>
       </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA367" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -66663,12 +67223,22 @@
       </c>
       <c r="AP367" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR367" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS367" t="inlineStr"/>
       <c r="AT367" t="n">
         <v>0</v>
+      </c>
+      <c r="AU367" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV367" t="inlineStr">
         <is>
@@ -67374,6 +67944,11 @@
       <c r="R372" t="n">
         <v>0</v>
       </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA372" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -67386,12 +67961,22 @@
       </c>
       <c r="AP372" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR372" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS372" t="inlineStr"/>
       <c r="AT372" t="n">
         <v>0</v>
+      </c>
+      <c r="AU372" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV372" t="inlineStr">
         <is>
@@ -68244,6 +68829,11 @@
       <c r="R378" t="n">
         <v>0</v>
       </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA378" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -68256,12 +68846,22 @@
       </c>
       <c r="AP378" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR378" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS378" t="inlineStr"/>
       <c r="AT378" t="n">
         <v>0</v>
+      </c>
+      <c r="AU378" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV378" t="inlineStr">
         <is>
@@ -68967,6 +69567,11 @@
       <c r="R383" t="n">
         <v>0</v>
       </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA383" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -68979,12 +69584,22 @@
       </c>
       <c r="AP383" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR383" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS383" t="inlineStr"/>
       <c r="AT383" t="n">
         <v>0</v>
+      </c>
+      <c r="AU383" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV383" t="inlineStr">
         <is>
@@ -69837,6 +70452,11 @@
       <c r="R389" t="n">
         <v>0</v>
       </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA389" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -69849,12 +70469,22 @@
       </c>
       <c r="AP389" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR389" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS389" t="inlineStr"/>
       <c r="AT389" t="n">
         <v>0</v>
+      </c>
+      <c r="AU389" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV389" t="inlineStr">
         <is>
@@ -70560,6 +71190,11 @@
       <c r="R394" t="n">
         <v>0</v>
       </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA394" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -70572,12 +71207,22 @@
       </c>
       <c r="AP394" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR394" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS394" t="inlineStr"/>
       <c r="AT394" t="n">
         <v>0</v>
+      </c>
+      <c r="AU394" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV394" t="inlineStr">
         <is>
@@ -71283,6 +71928,11 @@
       <c r="R399" t="n">
         <v>0</v>
       </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA399" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -71295,12 +71945,22 @@
       </c>
       <c r="AP399" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR399" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS399" t="inlineStr"/>
       <c r="AT399" t="n">
         <v>0</v>
+      </c>
+      <c r="AU399" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV399" t="inlineStr">
         <is>
@@ -72153,6 +72813,11 @@
       <c r="R405" t="n">
         <v>0</v>
       </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA405" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -72165,12 +72830,22 @@
       </c>
       <c r="AP405" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR405" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS405" t="inlineStr"/>
       <c r="AT405" t="n">
         <v>0</v>
+      </c>
+      <c r="AU405" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV405" t="inlineStr">
         <is>
@@ -72876,6 +73551,11 @@
       <c r="R410" t="n">
         <v>0</v>
       </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA410" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -72888,12 +73568,22 @@
       </c>
       <c r="AP410" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR410" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS410" t="inlineStr"/>
       <c r="AT410" t="n">
         <v>0</v>
+      </c>
+      <c r="AU410" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV410" t="inlineStr">
         <is>
@@ -73599,6 +74289,11 @@
       <c r="R415" t="n">
         <v>0</v>
       </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA415" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -73611,12 +74306,22 @@
       </c>
       <c r="AP415" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR415" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS415" t="inlineStr"/>
       <c r="AT415" t="n">
         <v>0</v>
+      </c>
+      <c r="AU415" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV415" t="inlineStr">
         <is>
@@ -74469,6 +75174,11 @@
       <c r="R421" t="n">
         <v>0</v>
       </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA421" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -74481,12 +75191,22 @@
       </c>
       <c r="AP421" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR421" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS421" t="inlineStr"/>
       <c r="AT421" t="n">
         <v>0</v>
+      </c>
+      <c r="AU421" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV421" t="inlineStr">
         <is>
